--- a/output/nabos_02_01avg.xlsx
+++ b/output/nabos_02_01avg.xlsx
@@ -544,7 +544,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.959</v>
+        <v>3.96</v>
       </c>
       <c r="B2" t="n">
         <v>74.11408</v>
@@ -556,64 +556,64 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.1294</v>
+        <v>-1.1295</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1295</v>
+        <v>-1.1292</v>
       </c>
       <c r="G2" t="n">
-        <v>22.130111</v>
+        <v>22.130482</v>
       </c>
       <c r="H2" t="n">
-        <v>22.129546</v>
+        <v>22.130995</v>
       </c>
       <c r="I2" t="n">
-        <v>26.9577</v>
+        <v>26.9583</v>
       </c>
       <c r="J2" t="n">
-        <v>26.957</v>
+        <v>26.9588</v>
       </c>
       <c r="K2" t="n">
-        <v>372.754</v>
+        <v>372.752</v>
       </c>
       <c r="L2" t="n">
-        <v>277.559</v>
+        <v>278.982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0778</v>
+        <v>0.0779</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5995</v>
+        <v>4.6001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.103</v>
+        <v>0.1027</v>
       </c>
       <c r="P2" t="n">
-        <v>0.103</v>
+        <v>0.1027</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0771</v>
+        <v>0.0766</v>
       </c>
       <c r="R2" t="n">
         <v>0.0281</v>
       </c>
       <c r="S2" t="n">
-        <v>5860</v>
+        <v>5858</v>
       </c>
       <c r="T2" t="n">
-        <v>4.0689</v>
+        <v>4.0676</v>
       </c>
       <c r="U2" t="n">
-        <v>45.71</v>
+        <v>45.67</v>
       </c>
       <c r="V2" t="n">
         <v>2.5858</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8359</v>
+        <v>1.8426</v>
       </c>
       <c r="X2" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -636,76 +636,76 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.948</v>
+        <v>4.944</v>
       </c>
       <c r="B3" t="n">
         <v>74.11406</v>
       </c>
       <c r="C3" t="n">
-        <v>168.68669</v>
+        <v>168.6867</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1304</v>
+        <v>-1.1305</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1291</v>
+        <v>-1.1294</v>
       </c>
       <c r="G3" t="n">
-        <v>22.126732</v>
+        <v>22.12646</v>
       </c>
       <c r="H3" t="n">
-        <v>22.125602</v>
+        <v>22.124956</v>
       </c>
       <c r="I3" t="n">
-        <v>26.9536</v>
+        <v>26.9534</v>
       </c>
       <c r="J3" t="n">
-        <v>26.9509</v>
+        <v>26.9503</v>
       </c>
       <c r="K3" t="n">
-        <v>372.678</v>
+        <v>372.661</v>
       </c>
       <c r="L3" t="n">
-        <v>284.294</v>
+        <v>285.495</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0661</v>
+        <v>0.0647</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6013</v>
+        <v>4.6012</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1023</v>
+        <v>0.1019</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1023</v>
+        <v>0.1019</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0755</v>
+        <v>0.0756</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0277</v>
+        <v>0.0276</v>
       </c>
       <c r="S3" t="n">
-        <v>6071</v>
+        <v>6098</v>
       </c>
       <c r="T3" t="n">
-        <v>4.2156</v>
+        <v>4.234</v>
       </c>
       <c r="U3" t="n">
-        <v>44.62</v>
+        <v>44.54</v>
       </c>
       <c r="V3" t="n">
-        <v>2.585</v>
+        <v>2.5849</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8676</v>
+        <v>1.8733</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.938</v>
+        <v>5.941</v>
       </c>
       <c r="B4" t="n">
         <v>74.11406</v>
@@ -746,34 +746,34 @@
         <v>-1.1299</v>
       </c>
       <c r="G4" t="n">
-        <v>22.128491</v>
+        <v>22.128263</v>
       </c>
       <c r="H4" t="n">
-        <v>22.125205</v>
+        <v>22.125303</v>
       </c>
       <c r="I4" t="n">
-        <v>26.9555</v>
+        <v>26.9552</v>
       </c>
       <c r="J4" t="n">
-        <v>26.9506</v>
+        <v>26.9508</v>
       </c>
       <c r="K4" t="n">
-        <v>372.706</v>
+        <v>372.696</v>
       </c>
       <c r="L4" t="n">
-        <v>283.7</v>
+        <v>283.751</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08</v>
+        <v>0.0795</v>
       </c>
       <c r="N4" t="n">
         <v>4.6006</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1027</v>
+        <v>0.1028</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1027</v>
+        <v>0.1028</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0761</v>
@@ -782,22 +782,22 @@
         <v>0.0282</v>
       </c>
       <c r="S4" t="n">
-        <v>6112</v>
+        <v>6114</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2441</v>
+        <v>4.2452</v>
       </c>
       <c r="U4" t="n">
-        <v>43.9</v>
+        <v>43.85</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5849</v>
+        <v>2.5848</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8646</v>
+        <v>1.8648</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6.927</v>
+        <v>6.923</v>
       </c>
       <c r="B5" t="n">
         <v>74.11406</v>
@@ -835,61 +835,61 @@
         <v>-1.129</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.129</v>
+        <v>-1.1292</v>
       </c>
       <c r="G5" t="n">
-        <v>22.128016</v>
+        <v>22.127873</v>
       </c>
       <c r="H5" t="n">
-        <v>22.126865</v>
+        <v>22.126709</v>
       </c>
       <c r="I5" t="n">
-        <v>26.953</v>
+        <v>26.9528</v>
       </c>
       <c r="J5" t="n">
         <v>26.9515</v>
       </c>
       <c r="K5" t="n">
-        <v>372.563</v>
+        <v>372.528</v>
       </c>
       <c r="L5" t="n">
-        <v>279.899</v>
+        <v>279.731</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0771</v>
+        <v>0.074</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6016</v>
+        <v>4.6014</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1016</v>
+        <v>0.1017</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1016</v>
+        <v>0.1017</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0753</v>
+        <v>0.0754</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0281</v>
+        <v>0.028</v>
       </c>
       <c r="S5" t="n">
-        <v>6169</v>
+        <v>6171</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2835</v>
+        <v>4.2846</v>
       </c>
       <c r="U5" t="n">
-        <v>42.66</v>
+        <v>42.62</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5839</v>
+        <v>2.5837</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8464</v>
+        <v>1.8456</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.917</v>
+        <v>7.92</v>
       </c>
       <c r="B6" t="n">
         <v>74.11406</v>
@@ -924,34 +924,34 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1292</v>
+        <v>-1.1294</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1297</v>
+        <v>-1.1298</v>
       </c>
       <c r="G6" t="n">
-        <v>22.127598</v>
+        <v>22.127593</v>
       </c>
       <c r="H6" t="n">
-        <v>22.124987</v>
+        <v>22.125057</v>
       </c>
       <c r="I6" t="n">
-        <v>26.9521</v>
+        <v>26.9523</v>
       </c>
       <c r="J6" t="n">
-        <v>26.9491</v>
+        <v>26.9493</v>
       </c>
       <c r="K6" t="n">
-        <v>372.661</v>
+        <v>372.644</v>
       </c>
       <c r="L6" t="n">
-        <v>281.292</v>
+        <v>281.407</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0927</v>
+        <v>0.0938</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6007</v>
+        <v>4.6003</v>
       </c>
       <c r="O6" t="n">
         <v>0.1016</v>
@@ -960,28 +960,28 @@
         <v>0.1016</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0761</v>
+        <v>0.0765</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0287</v>
+        <v>0.0288</v>
       </c>
       <c r="S6" t="n">
-        <v>6211</v>
+        <v>6213</v>
       </c>
       <c r="T6" t="n">
-        <v>4.3128</v>
+        <v>4.3138</v>
       </c>
       <c r="U6" t="n">
-        <v>41.7</v>
+        <v>41.66</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5841</v>
+        <v>2.584</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8528</v>
+        <v>1.8533</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.907</v>
+        <v>8.903</v>
       </c>
       <c r="B7" t="n">
         <v>74.11406</v>
@@ -1016,64 +1016,64 @@
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1372</v>
+        <v>-1.138</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1358</v>
+        <v>-1.1363</v>
       </c>
       <c r="G7" t="n">
-        <v>22.118773</v>
+        <v>22.117677</v>
       </c>
       <c r="H7" t="n">
-        <v>22.118743</v>
+        <v>22.118004</v>
       </c>
       <c r="I7" t="n">
-        <v>26.9471</v>
+        <v>26.9465</v>
       </c>
       <c r="J7" t="n">
-        <v>26.9457</v>
+        <v>26.9454</v>
       </c>
       <c r="K7" t="n">
-        <v>372.902</v>
+        <v>372.973</v>
       </c>
       <c r="L7" t="n">
-        <v>283.376</v>
+        <v>283.878</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0628</v>
+        <v>0.0621</v>
       </c>
       <c r="N7" t="n">
-        <v>4.601</v>
+        <v>4.6012</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1008</v>
+        <v>0.1007</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1008</v>
+        <v>0.1007</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0758</v>
+        <v>0.0756</v>
       </c>
       <c r="R7" t="n">
         <v>0.0275</v>
       </c>
       <c r="S7" t="n">
-        <v>6269</v>
+        <v>6271</v>
       </c>
       <c r="T7" t="n">
-        <v>4.3531</v>
+        <v>4.3541</v>
       </c>
       <c r="U7" t="n">
-        <v>40.56</v>
+        <v>40.52</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5846</v>
+        <v>2.585</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8622</v>
+        <v>1.8646</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1096,13 +1096,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9.896</v>
+        <v>9.9</v>
       </c>
       <c r="B8" t="n">
         <v>74.11406</v>
       </c>
       <c r="C8" t="n">
-        <v>168.68682</v>
+        <v>168.68683</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -1114,10 +1114,10 @@
         <v>-1.1364</v>
       </c>
       <c r="G8" t="n">
-        <v>22.119696</v>
+        <v>22.119601</v>
       </c>
       <c r="H8" t="n">
-        <v>22.118467</v>
+        <v>22.118303</v>
       </c>
       <c r="I8" t="n">
         <v>26.9474</v>
@@ -1126,16 +1126,16 @@
         <v>26.9453</v>
       </c>
       <c r="K8" t="n">
-        <v>372.891</v>
+        <v>372.878</v>
       </c>
       <c r="L8" t="n">
-        <v>284.489</v>
+        <v>284.824</v>
       </c>
       <c r="M8" t="n">
-        <v>0.066</v>
+        <v>0.0639</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6023</v>
+        <v>4.6024</v>
       </c>
       <c r="O8" t="n">
         <v>0.1018</v>
@@ -1144,28 +1144,28 @@
         <v>0.1018</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0747</v>
+        <v>0.0746</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0277</v>
+        <v>0.0276</v>
       </c>
       <c r="S8" t="n">
-        <v>6313</v>
+        <v>6314</v>
       </c>
       <c r="T8" t="n">
-        <v>4.3832</v>
+        <v>4.3838</v>
       </c>
       <c r="U8" t="n">
-        <v>39.76</v>
+        <v>39.73</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5843</v>
+        <v>2.5842</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8673</v>
+        <v>1.8689</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10.886</v>
+        <v>10.885</v>
       </c>
       <c r="B9" t="n">
         <v>74.11406</v>
@@ -1203,61 +1203,61 @@
         <v>-1.1365</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1361</v>
+        <v>-1.1362</v>
       </c>
       <c r="G9" t="n">
-        <v>22.120667</v>
+        <v>22.120549</v>
       </c>
       <c r="H9" t="n">
-        <v>22.119327</v>
+        <v>22.119331</v>
       </c>
       <c r="I9" t="n">
         <v>26.9479</v>
       </c>
       <c r="J9" t="n">
-        <v>26.9458</v>
+        <v>26.9459</v>
       </c>
       <c r="K9" t="n">
-        <v>372.588</v>
+        <v>372.587</v>
       </c>
       <c r="L9" t="n">
-        <v>295.81</v>
+        <v>296.492</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0597</v>
+        <v>0.0647</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6008</v>
+        <v>4.601</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1019</v>
+        <v>0.102</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1019</v>
+        <v>0.102</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0759</v>
+        <v>0.0758</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0274</v>
+        <v>0.0276</v>
       </c>
       <c r="S9" t="n">
-        <v>6370</v>
+        <v>6372</v>
       </c>
       <c r="T9" t="n">
-        <v>4.4231</v>
+        <v>4.4243</v>
       </c>
       <c r="U9" t="n">
-        <v>38.68</v>
+        <v>38.65</v>
       </c>
       <c r="V9" t="n">
         <v>2.5823</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9208</v>
+        <v>1.924</v>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11.875</v>
+        <v>11.876</v>
       </c>
       <c r="B10" t="n">
         <v>74.11406</v>
@@ -1301,22 +1301,22 @@
         <v>22.122376</v>
       </c>
       <c r="H10" t="n">
-        <v>22.121474</v>
+        <v>22.121374</v>
       </c>
       <c r="I10" t="n">
-        <v>26.9496</v>
+        <v>26.9497</v>
       </c>
       <c r="J10" t="n">
         <v>26.948</v>
       </c>
       <c r="K10" t="n">
-        <v>372.526</v>
+        <v>372.505</v>
       </c>
       <c r="L10" t="n">
-        <v>301.537</v>
+        <v>301.927</v>
       </c>
       <c r="M10" t="n">
-        <v>0.069</v>
+        <v>0.0643</v>
       </c>
       <c r="N10" t="n">
         <v>4.6019</v>
@@ -1331,25 +1331,25 @@
         <v>0.0751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0278</v>
+        <v>0.0276</v>
       </c>
       <c r="S10" t="n">
-        <v>6423</v>
+        <v>6425</v>
       </c>
       <c r="T10" t="n">
-        <v>4.4599</v>
+        <v>4.4609</v>
       </c>
       <c r="U10" t="n">
-        <v>37.7</v>
+        <v>37.66</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5817</v>
+        <v>2.5816</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9478</v>
+        <v>1.9496</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12.865</v>
+        <v>12.866</v>
       </c>
       <c r="B11" t="n">
         <v>74.11406</v>
@@ -1390,58 +1390,58 @@
         <v>-1.1365</v>
       </c>
       <c r="G11" t="n">
-        <v>22.126157</v>
+        <v>22.126302</v>
       </c>
       <c r="H11" t="n">
-        <v>22.12492</v>
+        <v>22.125087</v>
       </c>
       <c r="I11" t="n">
-        <v>26.9544</v>
+        <v>26.9547</v>
       </c>
       <c r="J11" t="n">
-        <v>26.9526</v>
+        <v>26.9528</v>
       </c>
       <c r="K11" t="n">
-        <v>372.837</v>
+        <v>372.808</v>
       </c>
       <c r="L11" t="n">
-        <v>305.211</v>
+        <v>304.272</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0654</v>
+        <v>0.0642</v>
       </c>
       <c r="N11" t="n">
         <v>4.6014</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1008</v>
+        <v>0.1006</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1008</v>
+        <v>0.1006</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0755</v>
+        <v>0.0754</v>
       </c>
       <c r="R11" t="n">
         <v>0.0276</v>
       </c>
       <c r="S11" t="n">
-        <v>6473</v>
+        <v>6475</v>
       </c>
       <c r="T11" t="n">
-        <v>4.4944</v>
+        <v>4.4957</v>
       </c>
       <c r="U11" t="n">
-        <v>36.74</v>
+        <v>36.69</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5833</v>
+        <v>2.5831</v>
       </c>
       <c r="W11" t="n">
-        <v>1.965</v>
+        <v>1.9606</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13.855</v>
+        <v>13.854</v>
       </c>
       <c r="B12" t="n">
         <v>74.11405</v>
@@ -1476,64 +1476,64 @@
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1378</v>
+        <v>-1.1379</v>
       </c>
       <c r="F12" t="n">
         <v>-1.1372</v>
       </c>
       <c r="G12" t="n">
-        <v>22.131851</v>
+        <v>22.131957</v>
       </c>
       <c r="H12" t="n">
-        <v>22.129959</v>
+        <v>22.130098</v>
       </c>
       <c r="I12" t="n">
-        <v>26.9625</v>
+        <v>26.9627</v>
       </c>
       <c r="J12" t="n">
-        <v>26.9594</v>
+        <v>26.9597</v>
       </c>
       <c r="K12" t="n">
-        <v>372.976</v>
+        <v>372.969</v>
       </c>
       <c r="L12" t="n">
-        <v>290.279</v>
+        <v>290.165</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0559</v>
+        <v>0.052</v>
       </c>
       <c r="N12" t="n">
         <v>4.6015</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0992</v>
+        <v>0.099</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0992</v>
+        <v>0.099</v>
       </c>
       <c r="Q12" t="n">
         <v>0.0754</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0272</v>
+        <v>0.0271</v>
       </c>
       <c r="S12" t="n">
-        <v>6531</v>
+        <v>6532</v>
       </c>
       <c r="T12" t="n">
-        <v>4.535</v>
+        <v>4.5358</v>
       </c>
       <c r="U12" t="n">
-        <v>35.72</v>
+        <v>35.71</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5839</v>
+        <v>2.5838</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8941</v>
+        <v>1.8936</v>
       </c>
       <c r="X12" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1568,64 +1568,64 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1405</v>
+        <v>-1.1406</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.14</v>
+        <v>-1.1401</v>
       </c>
       <c r="G13" t="n">
-        <v>22.1379</v>
+        <v>22.138005</v>
       </c>
       <c r="H13" t="n">
-        <v>22.136428</v>
+        <v>22.13646</v>
       </c>
       <c r="I13" t="n">
-        <v>26.9724</v>
+        <v>26.9728</v>
       </c>
       <c r="J13" t="n">
-        <v>26.97</v>
+        <v>26.9702</v>
       </c>
       <c r="K13" t="n">
-        <v>373.033</v>
+        <v>373.061</v>
       </c>
       <c r="L13" t="n">
-        <v>295.187</v>
+        <v>295.585</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0433</v>
+        <v>0.0478</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6015</v>
+        <v>4.6016</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1011</v>
+        <v>0.1012</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1011</v>
+        <v>0.1012</v>
       </c>
       <c r="Q13" t="n">
         <v>0.0753</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0267</v>
+        <v>0.0269</v>
       </c>
       <c r="S13" t="n">
-        <v>6585</v>
+        <v>6586</v>
       </c>
       <c r="T13" t="n">
-        <v>4.572</v>
+        <v>4.573</v>
       </c>
       <c r="U13" t="n">
-        <v>34.75</v>
+        <v>34.73</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5839</v>
+        <v>2.584</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9172</v>
+        <v>1.9191</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1666,58 +1666,58 @@
         <v>-1.1427</v>
       </c>
       <c r="G14" t="n">
-        <v>22.140404</v>
+        <v>22.140483</v>
       </c>
       <c r="H14" t="n">
-        <v>22.138974</v>
+        <v>22.139017</v>
       </c>
       <c r="I14" t="n">
-        <v>26.9778</v>
+        <v>26.9781</v>
       </c>
       <c r="J14" t="n">
-        <v>26.9753</v>
+        <v>26.9755</v>
       </c>
       <c r="K14" t="n">
-        <v>372.895</v>
+        <v>372.873</v>
       </c>
       <c r="L14" t="n">
-        <v>291.728</v>
+        <v>291.406</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0627</v>
+        <v>0.0617</v>
       </c>
       <c r="N14" t="n">
-        <v>4.601</v>
+        <v>4.6008</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0758</v>
+        <v>0.076</v>
       </c>
       <c r="R14" t="n">
         <v>0.0275</v>
       </c>
       <c r="S14" t="n">
-        <v>6634</v>
+        <v>6635</v>
       </c>
       <c r="T14" t="n">
-        <v>4.6061</v>
+        <v>4.6069</v>
       </c>
       <c r="U14" t="n">
-        <v>33.73</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5827</v>
+        <v>2.5826</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9006</v>
+        <v>1.899</v>
       </c>
       <c r="X14" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16.823</v>
+        <v>16.824</v>
       </c>
       <c r="B15" t="n">
         <v>74.11404</v>
@@ -1752,34 +1752,34 @@
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1588</v>
+        <v>-1.1593</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.158</v>
+        <v>-1.1587</v>
       </c>
       <c r="G15" t="n">
-        <v>22.141158</v>
+        <v>22.140534</v>
       </c>
       <c r="H15" t="n">
-        <v>22.13999</v>
+        <v>22.139277</v>
       </c>
       <c r="I15" t="n">
-        <v>26.9922</v>
+        <v>26.9924</v>
       </c>
       <c r="J15" t="n">
-        <v>26.99</v>
+        <v>26.9902</v>
       </c>
       <c r="K15" t="n">
-        <v>373.004</v>
+        <v>373.025</v>
       </c>
       <c r="L15" t="n">
-        <v>291.112</v>
+        <v>291.164</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0559</v>
+        <v>0.0512</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6008</v>
+        <v>4.6009</v>
       </c>
       <c r="O15" t="n">
         <v>0.1001</v>
@@ -1788,28 +1788,28 @@
         <v>0.1001</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0759</v>
+        <v>0.0758</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0273</v>
+        <v>0.0271</v>
       </c>
       <c r="S15" t="n">
-        <v>6684</v>
+        <v>6686</v>
       </c>
       <c r="T15" t="n">
-        <v>4.6409</v>
+        <v>4.6421</v>
       </c>
       <c r="U15" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5823</v>
+        <v>2.5824</v>
       </c>
       <c r="W15" t="n">
-        <v>1.897</v>
+        <v>1.8972</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1844,34 +1844,34 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1733</v>
+        <v>-1.1736</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1726</v>
+        <v>-1.173</v>
       </c>
       <c r="G16" t="n">
-        <v>22.16211</v>
+        <v>22.164795</v>
       </c>
       <c r="H16" t="n">
-        <v>22.160593</v>
+        <v>22.163226</v>
       </c>
       <c r="I16" t="n">
-        <v>27.0327</v>
+        <v>27.0375</v>
       </c>
       <c r="J16" t="n">
-        <v>27.0301</v>
+        <v>27.0348</v>
       </c>
       <c r="K16" t="n">
-        <v>373.151</v>
+        <v>373.136</v>
       </c>
       <c r="L16" t="n">
-        <v>275.596</v>
+        <v>273.723</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0658</v>
+        <v>0.0666</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5997</v>
+        <v>4.5996</v>
       </c>
       <c r="O16" t="n">
         <v>0.1001</v>
@@ -1880,28 +1880,28 @@
         <v>0.1001</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0769</v>
+        <v>0.077</v>
       </c>
       <c r="R16" t="n">
         <v>0.0277</v>
       </c>
       <c r="S16" t="n">
-        <v>6741</v>
+        <v>6742</v>
       </c>
       <c r="T16" t="n">
-        <v>4.6804</v>
+        <v>4.6814</v>
       </c>
       <c r="U16" t="n">
-        <v>31.57</v>
+        <v>31.55</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5826</v>
+        <v>2.5825</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8232</v>
+        <v>1.8143</v>
       </c>
       <c r="X16" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18.803</v>
+        <v>18.802</v>
       </c>
       <c r="B17" t="n">
         <v>74.11404</v>
@@ -1936,64 +1936,64 @@
         <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1765</v>
+        <v>-1.1751</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1768</v>
+        <v>-1.1756</v>
       </c>
       <c r="G17" t="n">
-        <v>22.304407</v>
+        <v>22.316779</v>
       </c>
       <c r="H17" t="n">
-        <v>22.302652</v>
+        <v>22.313254</v>
       </c>
       <c r="I17" t="n">
-        <v>27.2249</v>
+        <v>27.2408</v>
       </c>
       <c r="J17" t="n">
-        <v>27.2228</v>
+        <v>27.2366</v>
       </c>
       <c r="K17" t="n">
-        <v>372.699</v>
+        <v>372.632</v>
       </c>
       <c r="L17" t="n">
-        <v>268.766</v>
+        <v>269.502</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1265</v>
+        <v>0.1282</v>
       </c>
       <c r="N17" t="n">
         <v>4.5984</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1001</v>
+        <v>0.1002</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1001</v>
+        <v>0.1002</v>
       </c>
       <c r="Q17" t="n">
         <v>0.078</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03</v>
+        <v>0.0301</v>
       </c>
       <c r="S17" t="n">
-        <v>6794</v>
+        <v>6795</v>
       </c>
       <c r="T17" t="n">
-        <v>4.7173</v>
+        <v>4.7181</v>
       </c>
       <c r="U17" t="n">
-        <v>30.64</v>
+        <v>30.61</v>
       </c>
       <c r="V17" t="n">
         <v>2.5827</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7924</v>
+        <v>1.7961</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19.792</v>
+        <v>19.793</v>
       </c>
       <c r="B18" t="n">
         <v>74.11404</v>
@@ -2028,64 +2028,64 @@
         <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.994</v>
+        <v>-0.9904</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9963</v>
+        <v>-0.9928</v>
       </c>
       <c r="G18" t="n">
-        <v>23.29581</v>
+        <v>23.307532</v>
       </c>
       <c r="H18" t="n">
-        <v>23.28683</v>
+        <v>23.29869</v>
       </c>
       <c r="I18" t="n">
-        <v>28.3777</v>
+        <v>28.3847</v>
       </c>
       <c r="J18" t="n">
-        <v>28.3679</v>
+        <v>28.3752</v>
       </c>
       <c r="K18" t="n">
-        <v>367.904</v>
+        <v>367.914</v>
       </c>
       <c r="L18" t="n">
-        <v>269.18</v>
+        <v>269.062</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2904</v>
+        <v>0.2962</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5865</v>
+        <v>4.5858</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1038</v>
+        <v>0.1039</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1038</v>
+        <v>0.1039</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0884</v>
+        <v>0.089</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0366</v>
+        <v>0.0369</v>
       </c>
       <c r="S18" t="n">
-        <v>6845</v>
+        <v>6846</v>
       </c>
       <c r="T18" t="n">
-        <v>4.7528</v>
+        <v>4.7533</v>
       </c>
       <c r="U18" t="n">
-        <v>29.41</v>
+        <v>29.4</v>
       </c>
       <c r="V18" t="n">
-        <v>2.586</v>
+        <v>2.5864</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8129</v>
+        <v>1.8125</v>
       </c>
       <c r="X18" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20.782</v>
+        <v>20.781</v>
       </c>
       <c r="B19" t="n">
         <v>74.11404</v>
@@ -2120,34 +2120,34 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9009</v>
+        <v>-0.9008</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9003</v>
+        <v>-0.9002</v>
       </c>
       <c r="G19" t="n">
-        <v>23.624673</v>
+        <v>23.632544</v>
       </c>
       <c r="H19" t="n">
-        <v>23.624388</v>
+        <v>23.632312</v>
       </c>
       <c r="I19" t="n">
-        <v>28.7275</v>
+        <v>28.7316</v>
       </c>
       <c r="J19" t="n">
-        <v>28.7266</v>
+        <v>28.7308</v>
       </c>
       <c r="K19" t="n">
-        <v>370.113</v>
+        <v>370.281</v>
       </c>
       <c r="L19" t="n">
-        <v>266.87</v>
+        <v>266.262</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2591</v>
+        <v>0.258</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5455</v>
+        <v>4.5442</v>
       </c>
       <c r="O19" t="n">
         <v>0.1064</v>
@@ -2156,28 +2156,28 @@
         <v>0.1064</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1244</v>
+        <v>0.1255</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0354</v>
+        <v>0.0353</v>
       </c>
       <c r="S19" t="n">
-        <v>6897</v>
+        <v>6898</v>
       </c>
       <c r="T19" t="n">
-        <v>4.7889</v>
+        <v>4.7898</v>
       </c>
       <c r="U19" t="n">
-        <v>28.35</v>
+        <v>28.34</v>
       </c>
       <c r="V19" t="n">
-        <v>2.61</v>
+        <v>2.6111</v>
       </c>
       <c r="W19" t="n">
-        <v>1.809</v>
+        <v>1.8061</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2212,64 +2212,64 @@
         <v>22</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9205</v>
+        <v>-0.921</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9203</v>
+        <v>-0.9207</v>
       </c>
       <c r="G20" t="n">
-        <v>23.676461</v>
+        <v>23.680804</v>
       </c>
       <c r="H20" t="n">
-        <v>23.675655</v>
+        <v>23.680041</v>
       </c>
       <c r="I20" t="n">
-        <v>28.8149</v>
+        <v>28.817</v>
       </c>
       <c r="J20" t="n">
-        <v>28.8135</v>
+        <v>28.8157</v>
       </c>
       <c r="K20" t="n">
-        <v>377.629</v>
+        <v>377.805</v>
       </c>
       <c r="L20" t="n">
-        <v>257.818</v>
+        <v>257.39</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2289</v>
+        <v>0.2282</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5408</v>
+        <v>4.5403</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1061</v>
+        <v>0.106</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1061</v>
+        <v>0.106</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1285</v>
+        <v>0.129</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0342</v>
+        <v>0.0341</v>
       </c>
       <c r="S20" t="n">
-        <v>6948</v>
+        <v>6950</v>
       </c>
       <c r="T20" t="n">
-        <v>4.8246</v>
+        <v>4.8255</v>
       </c>
       <c r="U20" t="n">
-        <v>27.25</v>
+        <v>27.22</v>
       </c>
       <c r="V20" t="n">
-        <v>2.6529</v>
+        <v>2.6539</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7652</v>
+        <v>1.7631</v>
       </c>
       <c r="X20" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22.761</v>
+        <v>22.762</v>
       </c>
       <c r="B21" t="n">
         <v>74.11404</v>
@@ -2304,34 +2304,34 @@
         <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9784</v>
+        <v>-0.9796</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9796</v>
+        <v>-0.9808</v>
       </c>
       <c r="G21" t="n">
-        <v>23.701285</v>
+        <v>23.702586</v>
       </c>
       <c r="H21" t="n">
-        <v>23.700498</v>
+        <v>23.701708</v>
       </c>
       <c r="I21" t="n">
-        <v>28.903</v>
+        <v>28.9047</v>
       </c>
       <c r="J21" t="n">
-        <v>28.9031</v>
+        <v>28.9047</v>
       </c>
       <c r="K21" t="n">
-        <v>384.088</v>
+        <v>384.199</v>
       </c>
       <c r="L21" t="n">
-        <v>245.711</v>
+        <v>245.019</v>
       </c>
       <c r="M21" t="n">
-        <v>0.269</v>
+        <v>0.2674</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5569</v>
+        <v>4.5573</v>
       </c>
       <c r="O21" t="n">
         <v>0.1059</v>
@@ -2340,28 +2340,28 @@
         <v>0.1059</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1143</v>
+        <v>0.114</v>
       </c>
       <c r="R21" t="n">
         <v>0.0357</v>
       </c>
       <c r="S21" t="n">
-        <v>6999</v>
+        <v>7000</v>
       </c>
       <c r="T21" t="n">
-        <v>4.8594</v>
+        <v>4.8603</v>
       </c>
       <c r="U21" t="n">
-        <v>26.22</v>
+        <v>26.2</v>
       </c>
       <c r="V21" t="n">
-        <v>2.6873</v>
+        <v>2.6879</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7052</v>
+        <v>1.7018</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2384,76 +2384,76 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23.75</v>
+        <v>23.749</v>
       </c>
       <c r="B22" t="n">
         <v>74.11404</v>
       </c>
       <c r="C22" t="n">
-        <v>168.68726</v>
+        <v>168.68727</v>
       </c>
       <c r="D22" t="n">
         <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0221</v>
+        <v>-1.0244</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.022</v>
+        <v>-1.0241</v>
       </c>
       <c r="G22" t="n">
-        <v>23.711941</v>
+        <v>23.711239</v>
       </c>
       <c r="H22" t="n">
-        <v>23.71069</v>
+        <v>23.710034</v>
       </c>
       <c r="I22" t="n">
-        <v>28.9589</v>
+        <v>28.9606</v>
       </c>
       <c r="J22" t="n">
-        <v>28.957</v>
+        <v>28.9586</v>
       </c>
       <c r="K22" t="n">
-        <v>388.231</v>
+        <v>388.41</v>
       </c>
       <c r="L22" t="n">
-        <v>239.658</v>
+        <v>238.72</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2273</v>
+        <v>0.2274</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5599</v>
+        <v>4.5601</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1068</v>
+        <v>0.1069</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1068</v>
+        <v>0.1069</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1117</v>
+        <v>0.1116</v>
       </c>
       <c r="R22" t="n">
         <v>0.0341</v>
       </c>
       <c r="S22" t="n">
-        <v>7052</v>
+        <v>7053</v>
       </c>
       <c r="T22" t="n">
-        <v>4.8964</v>
+        <v>4.8975</v>
       </c>
       <c r="U22" t="n">
-        <v>25.18</v>
+        <v>25.15</v>
       </c>
       <c r="V22" t="n">
-        <v>2.7087</v>
+        <v>2.7096</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6748</v>
+        <v>1.6702</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24.74</v>
+        <v>24.741</v>
       </c>
       <c r="B23" t="n">
         <v>74.11402</v>
@@ -2488,31 +2488,31 @@
         <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0645</v>
+        <v>-1.0691</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0649</v>
+        <v>-1.0698</v>
       </c>
       <c r="G23" t="n">
-        <v>23.717547</v>
+        <v>23.713815</v>
       </c>
       <c r="H23" t="n">
-        <v>23.7161</v>
+        <v>23.712198</v>
       </c>
       <c r="I23" t="n">
-        <v>29.0068</v>
+        <v>29.0079</v>
       </c>
       <c r="J23" t="n">
-        <v>29.0052</v>
+        <v>29.0064</v>
       </c>
       <c r="K23" t="n">
-        <v>389.46</v>
+        <v>389.404</v>
       </c>
       <c r="L23" t="n">
-        <v>241.299</v>
+        <v>245.89</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2544</v>
+        <v>0.2668</v>
       </c>
       <c r="N23" t="n">
         <v>4.5607</v>
@@ -2527,25 +2527,25 @@
         <v>0.1111</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0352</v>
+        <v>0.0357</v>
       </c>
       <c r="S23" t="n">
-        <v>7098</v>
+        <v>7100</v>
       </c>
       <c r="T23" t="n">
-        <v>4.9288</v>
+        <v>4.9301</v>
       </c>
       <c r="U23" t="n">
-        <v>23.99</v>
+        <v>22.87</v>
       </c>
       <c r="V23" t="n">
-        <v>2.7134</v>
+        <v>2.7128</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6814</v>
+        <v>1.7034</v>
       </c>
       <c r="X23" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2568,76 +2568,76 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>25.729</v>
+        <v>25.728</v>
       </c>
       <c r="B24" t="n">
         <v>74.11402</v>
       </c>
       <c r="C24" t="n">
-        <v>168.68733</v>
+        <v>168.68732</v>
       </c>
       <c r="D24" t="n">
         <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1436</v>
+        <v>-1.1462</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.143</v>
+        <v>-1.1455</v>
       </c>
       <c r="G24" t="n">
-        <v>23.691951</v>
+        <v>23.68878</v>
       </c>
       <c r="H24" t="n">
-        <v>23.690545</v>
+        <v>23.687424</v>
       </c>
       <c r="I24" t="n">
-        <v>29.0484</v>
+        <v>29.0503</v>
       </c>
       <c r="J24" t="n">
-        <v>29.046</v>
+        <v>29.0478</v>
       </c>
       <c r="K24" t="n">
-        <v>389.922</v>
+        <v>389.931</v>
       </c>
       <c r="L24" t="n">
-        <v>278.977</v>
+        <v>282.588</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3465</v>
+        <v>0.3477</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5559</v>
+        <v>4.5553</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1108</v>
+        <v>0.1109</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1108</v>
+        <v>0.1109</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1152</v>
+        <v>0.1158</v>
       </c>
       <c r="R24" t="n">
         <v>0.0389</v>
       </c>
       <c r="S24" t="n">
-        <v>7154</v>
+        <v>7156</v>
       </c>
       <c r="T24" t="n">
-        <v>4.9672</v>
+        <v>4.9688</v>
       </c>
       <c r="U24" t="n">
-        <v>0.87</v>
+        <v>-0.88</v>
       </c>
       <c r="V24" t="n">
         <v>2.7111</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8601</v>
+        <v>1.8774</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26.719</v>
+        <v>26.721</v>
       </c>
       <c r="B25" t="n">
         <v>74.11402</v>
@@ -2672,64 +2672,64 @@
         <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1453</v>
+        <v>-1.1639</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1485</v>
+        <v>-1.1678</v>
       </c>
       <c r="G25" t="n">
-        <v>23.727482</v>
+        <v>23.713917</v>
       </c>
       <c r="H25" t="n">
-        <v>23.723972</v>
+        <v>23.709489</v>
       </c>
       <c r="I25" t="n">
-        <v>29.0973</v>
+        <v>29.1005</v>
       </c>
       <c r="J25" t="n">
-        <v>29.0956</v>
+        <v>29.0985</v>
       </c>
       <c r="K25" t="n">
-        <v>388.536</v>
+        <v>388.615</v>
       </c>
       <c r="L25" t="n">
-        <v>310.012</v>
+        <v>318.847</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2536</v>
+        <v>0.2456</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5594</v>
+        <v>4.5595</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1112</v>
+        <v>0.1113</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1112</v>
+        <v>0.1113</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1122</v>
+        <v>0.1121</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0351</v>
+        <v>0.0348</v>
       </c>
       <c r="S25" t="n">
-        <v>7202</v>
+        <v>7203</v>
       </c>
       <c r="T25" t="n">
-        <v>5.0004</v>
+        <v>5.0014</v>
       </c>
       <c r="U25" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V25" t="n">
-        <v>2.7037</v>
+        <v>2.7029</v>
       </c>
       <c r="W25" t="n">
-        <v>2.0089</v>
+        <v>2.0505</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27.708</v>
+        <v>27.706</v>
       </c>
       <c r="B26" t="n">
         <v>74.11402</v>
@@ -2764,64 +2764,64 @@
         <v>28</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.3207</v>
+        <v>-1.3295</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.32</v>
+        <v>-1.3285</v>
       </c>
       <c r="G26" t="n">
-        <v>23.649679</v>
+        <v>23.639574</v>
       </c>
       <c r="H26" t="n">
-        <v>23.64793</v>
+        <v>23.63816</v>
       </c>
       <c r="I26" t="n">
-        <v>29.1627</v>
+        <v>29.1649</v>
       </c>
       <c r="J26" t="n">
-        <v>29.1598</v>
+        <v>29.1619</v>
       </c>
       <c r="K26" t="n">
-        <v>385.289</v>
+        <v>385.303</v>
       </c>
       <c r="L26" t="n">
-        <v>375.81</v>
+        <v>379.396</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2733</v>
+        <v>0.2714</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5658</v>
+        <v>4.5657</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1153</v>
+        <v>0.1156</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1153</v>
+        <v>0.1156</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1066</v>
+        <v>0.1067</v>
       </c>
       <c r="R26" t="n">
         <v>0.0359</v>
       </c>
       <c r="S26" t="n">
-        <v>7261</v>
+        <v>7263</v>
       </c>
       <c r="T26" t="n">
-        <v>5.0415</v>
+        <v>5.0427</v>
       </c>
       <c r="U26" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="V26" t="n">
-        <v>2.6744</v>
+        <v>2.6739</v>
       </c>
       <c r="W26" t="n">
-        <v>2.3171</v>
+        <v>2.3339</v>
       </c>
       <c r="X26" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2856,64 +2856,64 @@
         <v>29</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.3507</v>
+        <v>-1.3509</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3498</v>
+        <v>-1.3501</v>
       </c>
       <c r="G27" t="n">
-        <v>23.665548</v>
+        <v>23.661961</v>
       </c>
       <c r="H27" t="n">
-        <v>23.66366</v>
+        <v>23.660029</v>
       </c>
       <c r="I27" t="n">
-        <v>29.213</v>
+        <v>29.2146</v>
       </c>
       <c r="J27" t="n">
-        <v>29.2096</v>
+        <v>29.2111</v>
       </c>
       <c r="K27" t="n">
-        <v>378.7</v>
+        <v>378.502</v>
       </c>
       <c r="L27" t="n">
-        <v>371.897</v>
+        <v>371.494</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2942</v>
+        <v>0.2959</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5625</v>
+        <v>4.5626</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1166</v>
+        <v>0.1167</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1166</v>
+        <v>0.1167</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1095</v>
+        <v>0.1094</v>
       </c>
       <c r="R27" t="n">
         <v>0.0368</v>
       </c>
       <c r="S27" t="n">
-        <v>7305</v>
+        <v>7306</v>
       </c>
       <c r="T27" t="n">
-        <v>5.0724</v>
+        <v>5.0731</v>
       </c>
       <c r="U27" t="n">
         <v>0.03</v>
       </c>
       <c r="V27" t="n">
-        <v>2.6356</v>
+        <v>2.6345</v>
       </c>
       <c r="W27" t="n">
-        <v>2.2972</v>
+        <v>2.2953</v>
       </c>
       <c r="X27" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29.687</v>
+        <v>29.69</v>
       </c>
       <c r="B28" t="n">
         <v>74.11402</v>
@@ -2948,64 +2948,64 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3613</v>
+        <v>-1.3616</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3607</v>
+        <v>-1.3609</v>
       </c>
       <c r="G28" t="n">
-        <v>23.705675</v>
+        <v>23.703494</v>
       </c>
       <c r="H28" t="n">
-        <v>23.70325</v>
+        <v>23.701277</v>
       </c>
       <c r="I28" t="n">
-        <v>29.2771</v>
+        <v>29.2796</v>
       </c>
       <c r="J28" t="n">
-        <v>29.2733</v>
+        <v>29.2759</v>
       </c>
       <c r="K28" t="n">
-        <v>370.253</v>
+        <v>369.673</v>
       </c>
       <c r="L28" t="n">
-        <v>365.163</v>
+        <v>364.595</v>
       </c>
       <c r="M28" t="n">
-        <v>0.379</v>
+        <v>0.3868</v>
       </c>
       <c r="N28" t="n">
-        <v>4.565</v>
+        <v>4.5656</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1175</v>
+        <v>0.1176</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1175</v>
+        <v>0.1176</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1072</v>
+        <v>0.1067</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0402</v>
+        <v>0.0405</v>
       </c>
       <c r="S28" t="n">
-        <v>7347</v>
+        <v>7350</v>
       </c>
       <c r="T28" t="n">
-        <v>5.1016</v>
+        <v>5.1036</v>
       </c>
       <c r="U28" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="V28" t="n">
-        <v>2.5879</v>
+        <v>2.5847</v>
       </c>
       <c r="W28" t="n">
-        <v>2.2651</v>
+        <v>2.2624</v>
       </c>
       <c r="X28" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30.677</v>
+        <v>30.675</v>
       </c>
       <c r="B29" t="n">
         <v>74.11402</v>
@@ -3040,34 +3040,34 @@
         <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.3755</v>
+        <v>-1.376</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.375</v>
+        <v>-1.3757</v>
       </c>
       <c r="G29" t="n">
-        <v>23.747449</v>
+        <v>23.745701</v>
       </c>
       <c r="H29" t="n">
-        <v>23.745727</v>
+        <v>23.744439</v>
       </c>
       <c r="I29" t="n">
-        <v>29.3472</v>
+        <v>29.3491</v>
       </c>
       <c r="J29" t="n">
-        <v>29.3443</v>
+        <v>29.3471</v>
       </c>
       <c r="K29" t="n">
-        <v>358.494</v>
+        <v>357.973</v>
       </c>
       <c r="L29" t="n">
-        <v>354.459</v>
+        <v>353.996</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3679</v>
+        <v>0.3659</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5617</v>
+        <v>4.5629</v>
       </c>
       <c r="O29" t="n">
         <v>0.1184</v>
@@ -3076,28 +3076,28 @@
         <v>0.1184</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1101</v>
+        <v>0.1091</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0397</v>
+        <v>0.0396</v>
       </c>
       <c r="S29" t="n">
-        <v>7413</v>
+        <v>7416</v>
       </c>
       <c r="T29" t="n">
-        <v>5.1475</v>
+        <v>5.1495</v>
       </c>
       <c r="U29" t="n">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="V29" t="n">
-        <v>2.5214</v>
+        <v>2.5184</v>
       </c>
       <c r="W29" t="n">
-        <v>2.2139</v>
+        <v>2.2116</v>
       </c>
       <c r="X29" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31.666</v>
+        <v>31.668</v>
       </c>
       <c r="B30" t="n">
         <v>74.11402</v>
@@ -3132,64 +3132,64 @@
         <v>32</v>
       </c>
       <c r="E30" t="n">
+        <v>-1.389</v>
+      </c>
+      <c r="F30" t="n">
         <v>-1.3885</v>
       </c>
-      <c r="F30" t="n">
-        <v>-1.388</v>
-      </c>
       <c r="G30" t="n">
-        <v>23.819911</v>
+        <v>23.819651</v>
       </c>
       <c r="H30" t="n">
-        <v>23.818204</v>
+        <v>23.817974</v>
       </c>
       <c r="I30" t="n">
-        <v>29.4575</v>
+        <v>29.461</v>
       </c>
       <c r="J30" t="n">
-        <v>29.4548</v>
+        <v>29.4582</v>
       </c>
       <c r="K30" t="n">
-        <v>351.969</v>
+        <v>351.843</v>
       </c>
       <c r="L30" t="n">
-        <v>347.896</v>
+        <v>347.709</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3137</v>
+        <v>0.3148</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5566</v>
+        <v>4.5567</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1176</v>
+        <v>0.1174</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1176</v>
+        <v>0.1174</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1146</v>
+        <v>0.1145</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0375</v>
+        <v>0.0376</v>
       </c>
       <c r="S30" t="n">
-        <v>7464</v>
+        <v>7465</v>
       </c>
       <c r="T30" t="n">
-        <v>5.1826</v>
+        <v>5.1836</v>
       </c>
       <c r="U30" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="V30" t="n">
-        <v>2.4851</v>
+        <v>2.4844</v>
       </c>
       <c r="W30" t="n">
-        <v>2.183</v>
+        <v>2.1822</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -3224,64 +3224,64 @@
         <v>33</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.4036</v>
+        <v>-1.4043</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.4031</v>
+        <v>-1.4038</v>
       </c>
       <c r="G31" t="n">
-        <v>23.90953</v>
+        <v>23.910684</v>
       </c>
       <c r="H31" t="n">
-        <v>23.909044</v>
+        <v>23.910288</v>
       </c>
       <c r="I31" t="n">
-        <v>29.5935</v>
+        <v>29.5984</v>
       </c>
       <c r="J31" t="n">
-        <v>29.5923</v>
+        <v>29.5974</v>
       </c>
       <c r="K31" t="n">
-        <v>347.896</v>
+        <v>347.784</v>
       </c>
       <c r="L31" t="n">
-        <v>343.927</v>
+        <v>343.449</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5536</v>
+        <v>0.5612</v>
       </c>
       <c r="N31" t="n">
-        <v>4.5583</v>
+        <v>4.5581</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1177</v>
+        <v>0.1178</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1177</v>
+        <v>0.1178</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1131</v>
+        <v>0.1133</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0471</v>
+        <v>0.0474</v>
       </c>
       <c r="S31" t="n">
-        <v>7527</v>
+        <v>7529</v>
       </c>
       <c r="T31" t="n">
-        <v>5.2266</v>
+        <v>5.2281</v>
       </c>
       <c r="U31" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V31" t="n">
-        <v>2.463</v>
+        <v>2.4624</v>
       </c>
       <c r="W31" t="n">
-        <v>2.1649</v>
+        <v>2.1626</v>
       </c>
       <c r="X31" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3316,64 +3316,64 @@
         <v>34</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.4079</v>
+        <v>-1.4092</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.4081</v>
+        <v>-1.4097</v>
       </c>
       <c r="G32" t="n">
-        <v>24.004119</v>
+        <v>24.005612</v>
       </c>
       <c r="H32" t="n">
-        <v>24.005008</v>
+        <v>24.007629</v>
       </c>
       <c r="I32" t="n">
-        <v>29.7256</v>
+        <v>29.7308</v>
       </c>
       <c r="J32" t="n">
-        <v>29.7269</v>
+        <v>29.734</v>
       </c>
       <c r="K32" t="n">
-        <v>333.896</v>
+        <v>332.697</v>
       </c>
       <c r="L32" t="n">
-        <v>263.669</v>
+        <v>256.657</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8582</v>
+        <v>0.8821</v>
       </c>
       <c r="N32" t="n">
-        <v>4.5539</v>
+        <v>4.5527</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1207</v>
+        <v>0.1204</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1207</v>
+        <v>0.1204</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0593</v>
+        <v>0.0603</v>
       </c>
       <c r="S32" t="n">
-        <v>7598</v>
+        <v>7601</v>
       </c>
       <c r="T32" t="n">
-        <v>5.2758</v>
+        <v>5.278</v>
       </c>
       <c r="U32" t="n">
-        <v>3.92</v>
+        <v>4.43</v>
       </c>
       <c r="V32" t="n">
-        <v>2.3852</v>
+        <v>2.3784</v>
       </c>
       <c r="W32" t="n">
-        <v>1.7817</v>
+        <v>1.7481</v>
       </c>
       <c r="X32" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3396,46 +3396,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34.635</v>
+        <v>34.634</v>
       </c>
       <c r="B33" t="n">
         <v>74.11402</v>
       </c>
       <c r="C33" t="n">
-        <v>168.68756</v>
+        <v>168.68757</v>
       </c>
       <c r="D33" t="n">
         <v>35</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.459</v>
+        <v>-1.4604</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.461</v>
+        <v>-1.4623</v>
       </c>
       <c r="G33" t="n">
-        <v>24.076262</v>
+        <v>24.077208</v>
       </c>
       <c r="H33" t="n">
-        <v>24.077087</v>
+        <v>24.077572</v>
       </c>
       <c r="I33" t="n">
-        <v>29.8742</v>
+        <v>29.8796</v>
       </c>
       <c r="J33" t="n">
-        <v>29.8773</v>
+        <v>29.8821</v>
       </c>
       <c r="K33" t="n">
-        <v>311.239</v>
+        <v>310.463</v>
       </c>
       <c r="L33" t="n">
-        <v>197.237</v>
+        <v>195.173</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0737</v>
+        <v>1.0753</v>
       </c>
       <c r="N33" t="n">
-        <v>4.5283</v>
+        <v>4.5274</v>
       </c>
       <c r="O33" t="n">
         <v>0.1193</v>
@@ -3444,28 +3444,28 @@
         <v>0.1193</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1395</v>
+        <v>0.1403</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0679</v>
+        <v>0.068</v>
       </c>
       <c r="S33" t="n">
-        <v>7675</v>
+        <v>7678</v>
       </c>
       <c r="T33" t="n">
-        <v>5.3292</v>
+        <v>5.3311</v>
       </c>
       <c r="U33" t="n">
-        <v>13.41</v>
+        <v>13.76</v>
       </c>
       <c r="V33" t="n">
-        <v>2.2558</v>
+        <v>2.2514</v>
       </c>
       <c r="W33" t="n">
-        <v>1.463</v>
+        <v>1.4531</v>
       </c>
       <c r="X33" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>35.624</v>
+        <v>35.625</v>
       </c>
       <c r="B34" t="n">
         <v>74.11402</v>
@@ -3500,64 +3500,64 @@
         <v>36</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.493</v>
+        <v>-1.4931</v>
       </c>
       <c r="F34" t="n">
         <v>-1.4928</v>
       </c>
       <c r="G34" t="n">
-        <v>24.121737</v>
+        <v>24.123369</v>
       </c>
       <c r="H34" t="n">
-        <v>24.119523</v>
+        <v>24.121282</v>
       </c>
       <c r="I34" t="n">
-        <v>29.9696</v>
+        <v>29.9745</v>
       </c>
       <c r="J34" t="n">
-        <v>29.9664</v>
+        <v>29.9713</v>
       </c>
       <c r="K34" t="n">
-        <v>296.19</v>
+        <v>295.493</v>
       </c>
       <c r="L34" t="n">
-        <v>175.456</v>
+        <v>174.848</v>
       </c>
       <c r="M34" t="n">
-        <v>1.095</v>
+        <v>1.0807</v>
       </c>
       <c r="N34" t="n">
-        <v>4.4865</v>
+        <v>4.4855</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1178</v>
+        <v>0.1177</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1178</v>
+        <v>0.1177</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1767</v>
+        <v>0.1776</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0688</v>
+        <v>0.0682</v>
       </c>
       <c r="S34" t="n">
-        <v>7749</v>
+        <v>7753</v>
       </c>
       <c r="T34" t="n">
-        <v>5.3808</v>
+        <v>5.3832</v>
       </c>
       <c r="U34" t="n">
-        <v>12.68</v>
+        <v>12.64</v>
       </c>
       <c r="V34" t="n">
-        <v>2.1699</v>
+        <v>2.166</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3583</v>
+        <v>1.3555</v>
       </c>
       <c r="X34" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3592,34 +3592,34 @@
         <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4955</v>
+        <v>-1.4954</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4941</v>
+        <v>-1.4944</v>
       </c>
       <c r="G35" t="n">
-        <v>24.156524</v>
+        <v>24.157136</v>
       </c>
       <c r="H35" t="n">
-        <v>24.156542</v>
+        <v>24.157108</v>
       </c>
       <c r="I35" t="n">
-        <v>30.019</v>
+        <v>30.0214</v>
       </c>
       <c r="J35" t="n">
-        <v>30.0176</v>
+        <v>30.0202</v>
       </c>
       <c r="K35" t="n">
-        <v>285.713</v>
+        <v>285.396</v>
       </c>
       <c r="L35" t="n">
-        <v>148.92</v>
+        <v>147.936</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0618</v>
+        <v>1.0587</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4282</v>
+        <v>4.4268</v>
       </c>
       <c r="O35" t="n">
         <v>0.1182</v>
@@ -3628,28 +3628,28 @@
         <v>0.1182</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2291</v>
+        <v>0.2304</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0675</v>
+        <v>0.0674</v>
       </c>
       <c r="S35" t="n">
-        <v>7834</v>
+        <v>7837</v>
       </c>
       <c r="T35" t="n">
-        <v>5.4395</v>
+        <v>5.4416</v>
       </c>
       <c r="U35" t="n">
-        <v>7.88</v>
+        <v>7.53</v>
       </c>
       <c r="V35" t="n">
-        <v>2.1108</v>
+        <v>2.109</v>
       </c>
       <c r="W35" t="n">
-        <v>1.2315</v>
+        <v>1.2268</v>
       </c>
       <c r="X35" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3684,64 +3684,64 @@
         <v>38</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.4857</v>
+        <v>-1.4848</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.4846</v>
+        <v>-1.4838</v>
       </c>
       <c r="G36" t="n">
-        <v>24.221662</v>
+        <v>24.22516</v>
       </c>
       <c r="H36" t="n">
-        <v>24.223623</v>
+        <v>24.226862</v>
       </c>
       <c r="I36" t="n">
-        <v>30.0973</v>
+        <v>30.1018</v>
       </c>
       <c r="J36" t="n">
-        <v>30.0989</v>
+        <v>30.1031</v>
       </c>
       <c r="K36" t="n">
-        <v>279.42</v>
+        <v>279.174</v>
       </c>
       <c r="L36" t="n">
-        <v>145.084</v>
+        <v>145.455</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0919</v>
+        <v>1.1017</v>
       </c>
       <c r="N36" t="n">
-        <v>4.4033</v>
+        <v>4.4028</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1182</v>
+        <v>0.1183</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1182</v>
+        <v>0.1183</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2517</v>
+        <v>0.2521</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0687</v>
+        <v>0.0691</v>
       </c>
       <c r="S36" t="n">
-        <v>7910</v>
+        <v>7914</v>
       </c>
       <c r="T36" t="n">
-        <v>5.4925</v>
+        <v>5.4949</v>
       </c>
       <c r="U36" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="V36" t="n">
-        <v>2.0764</v>
+        <v>2.0751</v>
       </c>
       <c r="W36" t="n">
-        <v>1.2137</v>
+        <v>1.2155</v>
       </c>
       <c r="X36" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3776,34 +3776,34 @@
         <v>39</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4637</v>
+        <v>-1.4626</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.462</v>
+        <v>-1.4611</v>
       </c>
       <c r="G37" t="n">
-        <v>24.424654</v>
+        <v>24.434447</v>
       </c>
       <c r="H37" t="n">
-        <v>24.436594</v>
+        <v>24.444204</v>
       </c>
       <c r="I37" t="n">
-        <v>30.351</v>
+        <v>30.363</v>
       </c>
       <c r="J37" t="n">
-        <v>30.3656</v>
+        <v>30.3748</v>
       </c>
       <c r="K37" t="n">
-        <v>270.081</v>
+        <v>269.647</v>
       </c>
       <c r="L37" t="n">
-        <v>256.066</v>
+        <v>259.954</v>
       </c>
       <c r="M37" t="n">
-        <v>1.0759</v>
+        <v>1.0716</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3831</v>
+        <v>4.3821</v>
       </c>
       <c r="O37" t="n">
         <v>0.1195</v>
@@ -3812,28 +3812,28 @@
         <v>0.1195</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
       <c r="R37" t="n">
-        <v>0.068</v>
+        <v>0.0679</v>
       </c>
       <c r="S37" t="n">
-        <v>7993</v>
+        <v>7997</v>
       </c>
       <c r="T37" t="n">
-        <v>5.5503</v>
+        <v>5.5527</v>
       </c>
       <c r="U37" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="V37" t="n">
-        <v>2.0274</v>
+        <v>2.0251</v>
       </c>
       <c r="W37" t="n">
-        <v>1.7487</v>
+        <v>1.7675</v>
       </c>
       <c r="X37" t="n">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3856,76 +3856,76 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>39.582</v>
+        <v>39.584</v>
       </c>
       <c r="B38" t="n">
         <v>74.11403</v>
       </c>
       <c r="C38" t="n">
-        <v>168.68771</v>
+        <v>168.68772</v>
       </c>
       <c r="D38" t="n">
         <v>40</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4441</v>
+        <v>-1.4446</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4437</v>
+        <v>-1.4442</v>
       </c>
       <c r="G38" t="n">
-        <v>24.73779</v>
+        <v>24.744775</v>
       </c>
       <c r="H38" t="n">
-        <v>24.734359</v>
+        <v>24.741532</v>
       </c>
       <c r="I38" t="n">
-        <v>30.7574</v>
+        <v>30.7668</v>
       </c>
       <c r="J38" t="n">
-        <v>30.7522</v>
+        <v>30.7619</v>
       </c>
       <c r="K38" t="n">
-        <v>255.024</v>
+        <v>253.949</v>
       </c>
       <c r="L38" t="n">
-        <v>254.741</v>
+        <v>252.189</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6769</v>
+        <v>0.66</v>
       </c>
       <c r="N38" t="n">
-        <v>4.3494</v>
+        <v>4.3485</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1241</v>
+        <v>0.1243</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1241</v>
+        <v>0.1243</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.301</v>
+        <v>0.3018</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0521</v>
+        <v>0.0514</v>
       </c>
       <c r="S38" t="n">
-        <v>8066</v>
+        <v>8069</v>
       </c>
       <c r="T38" t="n">
-        <v>5.6009</v>
+        <v>5.6028</v>
       </c>
       <c r="U38" t="n">
         <v>0.03</v>
       </c>
       <c r="V38" t="n">
-        <v>1.9471</v>
+        <v>1.9411</v>
       </c>
       <c r="W38" t="n">
-        <v>1.7465</v>
+        <v>1.7343</v>
       </c>
       <c r="X38" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40.572</v>
+        <v>40.573</v>
       </c>
       <c r="B39" t="n">
         <v>74.11406</v>
@@ -3960,64 +3960,64 @@
         <v>41</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4211</v>
+        <v>-1.4201</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4226</v>
+        <v>-1.4215</v>
       </c>
       <c r="G39" t="n">
-        <v>25.051234</v>
+        <v>25.06273</v>
       </c>
       <c r="H39" t="n">
-        <v>25.02817</v>
+        <v>25.039945</v>
       </c>
       <c r="I39" t="n">
-        <v>31.1608</v>
+        <v>31.175</v>
       </c>
       <c r="J39" t="n">
-        <v>31.1308</v>
+        <v>31.1453</v>
       </c>
       <c r="K39" t="n">
-        <v>184.541</v>
+        <v>177.256</v>
       </c>
       <c r="L39" t="n">
-        <v>185.026</v>
+        <v>179.669</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4581</v>
+        <v>0.4444</v>
       </c>
       <c r="N39" t="n">
-        <v>4.0836</v>
+        <v>4.0548</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1288</v>
+        <v>0.1287</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1288</v>
+        <v>0.1287</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.5579</v>
+        <v>0.586</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0433</v>
+        <v>0.0428</v>
       </c>
       <c r="S39" t="n">
-        <v>8699</v>
+        <v>8688</v>
       </c>
       <c r="T39" t="n">
-        <v>6.0401</v>
+        <v>6.0329</v>
       </c>
       <c r="U39" t="n">
-        <v>4.13</v>
+        <v>3.67</v>
       </c>
       <c r="V39" t="n">
-        <v>1.5487</v>
+        <v>1.5073</v>
       </c>
       <c r="W39" t="n">
-        <v>1.4134</v>
+        <v>1.3877</v>
       </c>
       <c r="X39" t="n">
-        <v>29</v>
+        <v>368</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -4043,73 +4043,73 @@
         <v>41.561</v>
       </c>
       <c r="B40" t="n">
-        <v>74.11411</v>
+        <v>74.11412</v>
       </c>
       <c r="C40" t="n">
-        <v>168.68817</v>
+        <v>168.68818</v>
       </c>
       <c r="D40" t="n">
         <v>42</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3945</v>
+        <v>-1.3929</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3948</v>
+        <v>-1.3931</v>
       </c>
       <c r="G40" t="n">
-        <v>25.44757</v>
+        <v>25.470675</v>
       </c>
       <c r="H40" t="n">
-        <v>25.435058</v>
+        <v>25.460758</v>
       </c>
       <c r="I40" t="n">
-        <v>31.6737</v>
+        <v>31.7033</v>
       </c>
       <c r="J40" t="n">
-        <v>31.6569</v>
+        <v>31.6899</v>
       </c>
       <c r="K40" t="n">
-        <v>127.867</v>
+        <v>125.866</v>
       </c>
       <c r="L40" t="n">
-        <v>123.883</v>
+        <v>123.446</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2856</v>
+        <v>0.281</v>
       </c>
       <c r="N40" t="n">
-        <v>3.5396</v>
+        <v>3.5198</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1352</v>
+        <v>0.1356</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1352</v>
+        <v>0.1356</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.1315</v>
+        <v>1.1521</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
       <c r="S40" t="n">
-        <v>9709</v>
+        <v>9751</v>
       </c>
       <c r="T40" t="n">
-        <v>6.7417</v>
+        <v>6.7709</v>
       </c>
       <c r="U40" t="n">
-        <v>6.42</v>
+        <v>6.53</v>
       </c>
       <c r="V40" t="n">
-        <v>1.228</v>
+        <v>1.2168</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1208</v>
+        <v>1.1189</v>
       </c>
       <c r="X40" t="n">
-        <v>24</v>
+        <v>196</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -4132,76 +4132,76 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42.551</v>
+        <v>42.558</v>
       </c>
       <c r="B41" t="n">
-        <v>74.11413</v>
+        <v>74.11412</v>
       </c>
       <c r="C41" t="n">
-        <v>168.68825</v>
+        <v>168.68826</v>
       </c>
       <c r="D41" t="n">
         <v>43</v>
       </c>
       <c r="E41" t="n">
+        <v>-1.3851</v>
+      </c>
+      <c r="F41" t="n">
         <v>-1.385</v>
       </c>
-      <c r="F41" t="n">
-        <v>-1.3849</v>
-      </c>
       <c r="G41" t="n">
-        <v>25.606693</v>
+        <v>25.605525</v>
       </c>
       <c r="H41" t="n">
-        <v>25.606548</v>
+        <v>25.604251</v>
       </c>
       <c r="I41" t="n">
-        <v>31.8807</v>
+        <v>31.8789</v>
       </c>
       <c r="J41" t="n">
-        <v>31.8804</v>
+        <v>31.877</v>
       </c>
       <c r="K41" t="n">
-        <v>106.916</v>
+        <v>106.723</v>
       </c>
       <c r="L41" t="n">
-        <v>70.089</v>
+        <v>68.164</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4057</v>
+        <v>0.3743</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1318</v>
+        <v>3.1279</v>
       </c>
       <c r="O41" t="n">
-        <v>0.144</v>
+        <v>0.1442</v>
       </c>
       <c r="P41" t="n">
-        <v>0.144</v>
+        <v>0.1442</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.5992</v>
+        <v>1.604</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0413</v>
+        <v>0.04</v>
       </c>
       <c r="S41" t="n">
-        <v>9961</v>
+        <v>9967</v>
       </c>
       <c r="T41" t="n">
-        <v>6.9167</v>
+        <v>6.9209</v>
       </c>
       <c r="U41" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="V41" t="n">
-        <v>1.1087</v>
+        <v>1.1076</v>
       </c>
       <c r="W41" t="n">
-        <v>0.8602</v>
+        <v>0.8508</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
